--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F485F754-2327-45BC-B721-52C14C593F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10423260-2023-41BF-90FC-5BD7107B2575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="14">
   <si>
     <t>None</t>
   </si>
@@ -75,13 +75,16 @@
   </si>
   <si>
     <t>Music Sound Test</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,8 +113,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,6 +138,11 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -138,19 +153,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="3" builtinId="26"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -485,22 +503,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF0422-255B-404C-AE6B-B5A828AC21C0}">
   <dimension ref="A13:Y83"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="24.75" customWidth="1"/>
-    <col min="22" max="22" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="22" max="22" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:22" ht="36">
+    <row r="13" spans="1:22" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -519,13 +537,16 @@
       <c r="F14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>A15+1</f>
         <v>2</v>
@@ -534,7 +555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
@@ -542,7 +563,7 @@
       <c r="V17" s="2">
         <v>1</v>
       </c>
-      <c r="W17" s="1" t="s">
+      <c r="W17" s="4" t="s">
         <v>0</v>
       </c>
       <c r="X17" s="1" t="s">
@@ -552,7 +573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -571,7 +592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -590,7 +611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -609,7 +630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -628,7 +649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -647,7 +668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -666,7 +687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -685,7 +706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -704,7 +725,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -723,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -742,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -761,7 +782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -780,7 +801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -799,7 +820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -818,7 +839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
@@ -837,7 +858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="V33" s="1">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -852,7 +873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="V34" s="1">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -867,12 +888,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="36">
+    <row r="39" spans="1:25" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -891,120 +912,123 @@
       <c r="F40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:25">
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
         <f>A41+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" ref="A43:A57" si="2">A42+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
         <f>A57+1</f>
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="36">
+    <row r="64" spans="1:1" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1023,109 +1047,112 @@
       <c r="F65" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <f>A66+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <f t="shared" ref="A68:A82" si="3">A67+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>A82+1</f>
         <v>18</v>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10423260-2023-41BF-90FC-5BD7107B2575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E2E3A2-A993-48EA-9830-23A52B200E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
+    <workbookView xWindow="17805" yWindow="1260" windowWidth="27825" windowHeight="15345" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="18">
   <si>
     <t>None</t>
   </si>
@@ -78,13 +78,25 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>Time (Seconds)</t>
+  </si>
+  <si>
+    <t>Rating(1-100)</t>
+  </si>
+  <si>
+    <t>Immersion Rating</t>
+  </si>
+  <si>
+    <t>Sensitivity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,23 +514,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF0422-255B-404C-AE6B-B5A828AC21C0}">
-  <dimension ref="A13:Y83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A13:Z83"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="22" max="22" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="24.75" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="35.625" customWidth="1"/>
+    <col min="22" max="22" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:22" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:26" ht="34.5">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -538,70 +553,133 @@
         <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>1315</v>
+      </c>
+      <c r="C15">
+        <v>78</v>
+      </c>
+      <c r="D15">
+        <v>88.460999999999999</v>
+      </c>
+      <c r="E15">
+        <v>85.897000000000006</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15">
+        <v>90</v>
+      </c>
+      <c r="H15">
+        <v>50</v>
+      </c>
+      <c r="I15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16">
         <f>A15+1</f>
         <v>2</v>
       </c>
+      <c r="B16">
+        <v>1950</v>
+      </c>
+      <c r="C16">
+        <v>105</v>
+      </c>
+      <c r="D16">
+        <v>94.284999999999997</v>
+      </c>
+      <c r="E16">
+        <v>94.284999999999997</v>
+      </c>
+      <c r="F16">
+        <v>34</v>
+      </c>
+      <c r="G16">
+        <v>50</v>
+      </c>
+      <c r="H16">
+        <v>50</v>
+      </c>
+      <c r="I16">
+        <v>35</v>
+      </c>
       <c r="V16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17">
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
       </c>
-      <c r="V17" s="2">
+      <c r="V17" s="4">
         <v>1</v>
       </c>
       <c r="W17" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="X17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="X17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z17">
+        <v>0.68799999999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="V18" s="1">
+      <c r="V18" s="4">
         <f>V17+1</f>
         <v>2</v>
       </c>
-      <c r="W18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>0.374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="V19" s="1">
+      <c r="V19" s="2">
         <f t="shared" ref="V19:V34" si="1">V18+1</f>
         <v>3</v>
       </c>
-      <c r="W19" s="1" t="s">
+      <c r="W19" s="2" t="s">
         <v>1</v>
       </c>
       <c r="X19" s="1" t="s">
@@ -611,7 +689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -630,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -649,7 +727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -668,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -687,7 +765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -706,7 +784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -725,7 +803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -744,7 +822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -763,7 +841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -782,7 +860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -801,7 +879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -820,7 +898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -839,7 +917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
@@ -858,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25">
       <c r="V33" s="1">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -873,7 +951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25">
       <c r="V34" s="1">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -888,12 +966,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:25" ht="34.5">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -915,120 +993,174 @@
       <c r="G40" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>1385</v>
+      </c>
+      <c r="C41">
+        <v>73</v>
+      </c>
+      <c r="D41">
+        <v>95.89</v>
+      </c>
+      <c r="E41">
+        <v>95.89</v>
+      </c>
+      <c r="F41">
+        <v>31</v>
+      </c>
+      <c r="G41">
+        <v>50</v>
+      </c>
+      <c r="H41">
+        <v>60</v>
+      </c>
+      <c r="I41">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42">
         <f>A41+1</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>2200</v>
+      </c>
+      <c r="C42">
+        <v>118</v>
+      </c>
+      <c r="D42">
+        <v>94.915000000000006</v>
+      </c>
+      <c r="E42">
+        <v>94.066999999999993</v>
+      </c>
+      <c r="F42">
+        <v>37</v>
+      </c>
+      <c r="G42">
+        <v>40</v>
+      </c>
+      <c r="H42">
+        <v>58</v>
+      </c>
+      <c r="I42">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43">
         <f t="shared" ref="A43:A57" si="2">A42+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25">
       <c r="A44">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25">
       <c r="A45">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25">
       <c r="A46">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25">
       <c r="A47">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25">
       <c r="A48">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1">
       <c r="A56">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1">
       <c r="A57">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58">
         <f>A57+1</f>
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:1" ht="34.5">
       <c r="A64" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1050,109 +1182,163 @@
       <c r="G65" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>1550</v>
+      </c>
+      <c r="C66">
+        <v>82</v>
+      </c>
+      <c r="D66">
+        <v>96.340999999999994</v>
+      </c>
+      <c r="E66">
+        <v>95.120999999999995</v>
+      </c>
+      <c r="F66">
+        <v>16</v>
+      </c>
+      <c r="G66">
+        <v>60</v>
+      </c>
+      <c r="H66">
+        <v>80</v>
+      </c>
+      <c r="I66">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67">
         <f>A66+1</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>2165</v>
+      </c>
+      <c r="C67">
+        <v>122</v>
+      </c>
+      <c r="D67">
+        <v>90.98</v>
+      </c>
+      <c r="E67">
+        <v>90.98</v>
+      </c>
+      <c r="F67">
+        <v>40</v>
+      </c>
+      <c r="G67">
+        <v>40</v>
+      </c>
+      <c r="H67">
+        <v>60</v>
+      </c>
+      <c r="I67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68">
         <f t="shared" ref="A68:A82" si="3">A67+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1">
       <c r="A81">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1">
       <c r="A82">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1">
       <c r="A83">
         <f>A82+1</f>
         <v>18</v>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E2E3A2-A993-48EA-9830-23A52B200E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7579FB5-1E05-4D09-90E7-29C5D7B7C29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17805" yWindow="1260" windowWidth="27825" windowHeight="15345" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,13 +107,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -133,7 +126,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,11 +136,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -165,23 +153,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
-    <cellStyle name="Good" xfId="3" builtinId="26"/>
-    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -528,8 +514,8 @@
     <col min="22" max="22" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:26" ht="34.5">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:26" ht="36">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -632,16 +618,40 @@
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
       </c>
-      <c r="V17" s="4">
-        <v>1</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="4" t="s">
+      <c r="B17">
+        <v>1460</v>
+      </c>
+      <c r="C17">
+        <v>77</v>
+      </c>
+      <c r="D17">
+        <v>97.4</v>
+      </c>
+      <c r="E17">
+        <v>93.5</v>
+      </c>
+      <c r="F17">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>45</v>
+      </c>
+      <c r="H17">
+        <v>30</v>
+      </c>
+      <c r="I17">
+        <v>40</v>
+      </c>
+      <c r="V17" s="3">
+        <v>1</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Z17">
@@ -653,17 +663,41 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="V18" s="4">
+      <c r="B18">
+        <v>1945</v>
+      </c>
+      <c r="C18">
+        <v>106</v>
+      </c>
+      <c r="D18">
+        <v>93.396000000000001</v>
+      </c>
+      <c r="E18">
+        <v>93.396000000000001</v>
+      </c>
+      <c r="F18">
+        <v>52</v>
+      </c>
+      <c r="G18">
+        <v>15</v>
+      </c>
+      <c r="H18">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <v>20</v>
+      </c>
+      <c r="V18" s="3">
         <f>V17+1</f>
         <v>2</v>
       </c>
-      <c r="W18" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="X18" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y18" s="4" t="s">
+      <c r="W18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="3" t="s">
         <v>1</v>
       </c>
       <c r="Z18">
@@ -671,22 +705,49 @@
       </c>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19">
+      <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="V19" s="2">
+      <c r="B19" s="1">
+        <v>1805</v>
+      </c>
+      <c r="C19" s="1">
+        <v>118</v>
+      </c>
+      <c r="D19" s="1">
+        <v>87.287999999999997</v>
+      </c>
+      <c r="E19" s="1">
+        <v>72.033000000000001</v>
+      </c>
+      <c r="F19" s="1">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1">
+        <v>20</v>
+      </c>
+      <c r="H19" s="1">
+        <v>40</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="V19" s="3">
         <f t="shared" ref="V19:V34" si="1">V18+1</f>
         <v>3</v>
       </c>
-      <c r="W19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>2</v>
+      <c r="W19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z19">
+        <v>0.32800000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -694,18 +755,21 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="V20" s="1">
+      <c r="V20" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="W20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>0</v>
+      <c r="W20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0.47299999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:26">
@@ -713,18 +777,21 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="V21" s="1">
+      <c r="V21" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="W21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>1</v>
+      <c r="W21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="22" spans="1:26">
@@ -967,7 +1034,7 @@
       </c>
     </row>
     <row r="39" spans="1:25" ht="34.5">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1064,17 +1131,89 @@
         <f t="shared" ref="A43:A57" si="2">A42+1</f>
         <v>3</v>
       </c>
+      <c r="B43">
+        <v>1570</v>
+      </c>
+      <c r="C43">
+        <v>87</v>
+      </c>
+      <c r="D43">
+        <v>95.402000000000001</v>
+      </c>
+      <c r="E43">
+        <v>87.355999999999995</v>
+      </c>
+      <c r="F43">
+        <v>16</v>
+      </c>
+      <c r="G43">
+        <v>60</v>
+      </c>
+      <c r="H43">
+        <v>55</v>
+      </c>
+      <c r="I43">
+        <v>80</v>
+      </c>
     </row>
     <row r="44" spans="1:25">
       <c r="A44">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
+      <c r="B44">
+        <v>1830</v>
+      </c>
+      <c r="C44">
+        <v>99</v>
+      </c>
+      <c r="D44">
+        <v>95.959000000000003</v>
+      </c>
+      <c r="E44">
+        <v>90.909000000000006</v>
+      </c>
+      <c r="F44">
+        <v>37</v>
+      </c>
+      <c r="G44">
+        <v>30</v>
+      </c>
+      <c r="H44">
+        <v>39</v>
+      </c>
+      <c r="I44">
+        <v>40</v>
+      </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45">
+      <c r="A45" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2050</v>
+      </c>
+      <c r="C45" s="1">
+        <v>122</v>
+      </c>
+      <c r="D45" s="1">
+        <v>88.524000000000001</v>
+      </c>
+      <c r="E45" s="1">
+        <v>88.524000000000001</v>
+      </c>
+      <c r="F45" s="1">
+        <v>20</v>
+      </c>
+      <c r="G45" s="1">
+        <v>25</v>
+      </c>
+      <c r="H45" s="1">
+        <v>95</v>
+      </c>
+      <c r="I45" s="1">
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -1156,7 +1295,7 @@
       </c>
     </row>
     <row r="64" spans="1:1" ht="34.5">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1253,17 +1392,89 @@
         <f t="shared" ref="A68:A82" si="3">A67+1</f>
         <v>3</v>
       </c>
+      <c r="B68">
+        <v>1520</v>
+      </c>
+      <c r="C68">
+        <v>86</v>
+      </c>
+      <c r="D68">
+        <v>93.022999999999996</v>
+      </c>
+      <c r="E68" s="4">
+        <v>87.209000000000003</v>
+      </c>
+      <c r="F68">
+        <v>23</v>
+      </c>
+      <c r="G68">
+        <v>45</v>
+      </c>
+      <c r="H68">
+        <v>70</v>
+      </c>
+      <c r="I68">
+        <v>80</v>
+      </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
+      <c r="B69">
+        <v>1910</v>
+      </c>
+      <c r="C69">
+        <v>104</v>
+      </c>
+      <c r="D69">
+        <v>94.23</v>
+      </c>
+      <c r="E69">
+        <v>92.307000000000002</v>
+      </c>
+      <c r="F69">
+        <v>27</v>
+      </c>
+      <c r="G69">
+        <v>20</v>
+      </c>
+      <c r="H69">
+        <v>60</v>
+      </c>
+      <c r="I69">
+        <v>55</v>
+      </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70">
+      <c r="A70" s="1">
         <f t="shared" si="3"/>
         <v>5</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1905</v>
+      </c>
+      <c r="C70" s="1">
+        <v>109</v>
+      </c>
+      <c r="D70" s="1">
+        <v>89.908000000000001</v>
+      </c>
+      <c r="E70" s="1">
+        <v>89.908000000000001</v>
+      </c>
+      <c r="F70" s="1">
+        <v>30</v>
+      </c>
+      <c r="G70" s="1">
+        <v>30</v>
+      </c>
+      <c r="H70" s="1">
+        <v>80</v>
+      </c>
+      <c r="I70" s="1">
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:9">

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,71 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39394E3B-831F-4424-8F3C-FC86B683B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6503BBBA-8B88-4E8A-B810-ACE076FEE94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$14</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$15:$B$19</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$C$14</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$C$15:$C$19</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$B$14</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$B$15:$B$19</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$B$14:$B$19</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$V$15:$V$19</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$AC$14</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$AC$15:$AC$19</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$I$14</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$I$15:$I$19</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$AC$14</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$S$14</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$S$15:$S$19</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$AC$14</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$AC$15:$AC$19</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$I$14</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$I$15:$I$19</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$S$14</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$S$15:$S$19</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Sheet1!$AC$14</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Sheet1!$AC$15:$AC$19</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$AC$15:$AC$19</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Sheet1!$I$14</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Sheet1!$I$15:$I$19</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Sheet1!$S$14</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Sheet1!$S$15:$S$19</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Sheet1!$B$14</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Sheet1!$B$15:$B$19</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Sheet1!$L$14</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Sheet1!$L$15:$L$19</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Sheet1!$V$14</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Sheet1!$V$15:$V$19</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$I$14</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Sheet1!$C$14</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Sheet1!$C$15:$C$19</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Sheet1!$M$14</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Sheet1!$M$15:$M$19</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Sheet1!$W$14</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Sheet1!$W$15:$W$19</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Sheet1!$B$14</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Sheet1!$B$15:$B$19</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">Sheet1!$L$14</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">Sheet1!$L$15:$L$19</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$I$15:$I$19</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">Sheet1!$V$14</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">Sheet1!$V$15:$V$19</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">Sheet1!$B$14</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">Sheet1!$B$15:$B$19</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">Sheet1!$L$14</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">Sheet1!$L$15:$L$19</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$S$14</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$S$15:$S$19</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$B$14</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$B$15:$B$19</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -94,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="23">
   <si>
     <t>None</t>
   </si>
@@ -154,13 +96,22 @@
   </si>
   <si>
     <t>Score 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>I prefered the feedback from the middle one, it felt more fun and engaging, I knew what was going on and could lock in a lot more than with no sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I found the music fun but could sense it took me out of the game a little bit due to the "fantasy feel", but could see it working in other settings more. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,8 +140,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,6 +165,11 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -217,21 +180,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -248,58 +214,106 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D0D15333-C67E-40DC-AC5A-B9316DF0BF18}" name="Table2" displayName="Table2" ref="A14:I32" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D0D15333-C67E-40DC-AC5A-B9316DF0BF18}" name="Table2" displayName="Table2" ref="A14:I33" totalsRowCount="1">
   <autoFilter ref="A14:I32" xr:uid="{D0D15333-C67E-40DC-AC5A-B9316DF0BF18}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{C2071BA2-A7DC-42D4-98FA-F92AB6099EAF}" name="#">
       <calculatedColumnFormula>A14+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FC3CEE07-0ADF-4211-A4E2-7FB53197A7BE}" name="Score 1"/>
-    <tableColumn id="3" xr3:uid="{5A3DD35F-CF6B-441E-B2B9-79AD42013981}" name="Total Shots"/>
-    <tableColumn id="4" xr3:uid="{1409ED81-94DC-4733-82F2-6CF126CC1CA0}" name="Accuracy (%)"/>
-    <tableColumn id="5" xr3:uid="{D51B61C7-E976-458D-A6CB-5B9CE213BE17}" name="Headshot (%)"/>
-    <tableColumn id="6" xr3:uid="{AC663478-E2E7-45E7-8191-83A43E4EB776}" name="Max Headshots in a Row"/>
-    <tableColumn id="7" xr3:uid="{2CE36111-4B5E-46EA-A7BA-B1AB56B38BBE}" name="Time (Seconds)"/>
-    <tableColumn id="8" xr3:uid="{6FAED585-454C-43E9-BFC4-C4F43B8C0EF8}" name="Rating(1-100)"/>
-    <tableColumn id="9" xr3:uid="{AD51AF64-3555-4134-A1DA-DFDC71A1E8E1}" name="Immersion Rating"/>
+    <tableColumn id="2" xr3:uid="{FC3CEE07-0ADF-4211-A4E2-7FB53197A7BE}" name="Score 1" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(B15:B32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{5A3DD35F-CF6B-441E-B2B9-79AD42013981}" name="Total Shots" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(C15:C32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{1409ED81-94DC-4733-82F2-6CF126CC1CA0}" name="Accuracy (%)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(D15:D32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{D51B61C7-E976-458D-A6CB-5B9CE213BE17}" name="Headshot (%)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(E15:E32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{AC663478-E2E7-45E7-8191-83A43E4EB776}" name="Max Headshots in a Row" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(F15:F32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{2CE36111-4B5E-46EA-A7BA-B1AB56B38BBE}" name="Time (Seconds)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(G15:G32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{6FAED585-454C-43E9-BFC4-C4F43B8C0EF8}" name="Rating(1-100)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(H15:H32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{AD51AF64-3555-4134-A1DA-DFDC71A1E8E1}" name="Immersion Rating" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(I15:I32)</totalsRowFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A27FC0ED-52DB-43A2-8404-294B98E570CF}" name="Table3" displayName="Table3" ref="K14:S32" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A27FC0ED-52DB-43A2-8404-294B98E570CF}" name="Table3" displayName="Table3" ref="K14:S33" totalsRowCount="1">
   <autoFilter ref="K14:S32" xr:uid="{A27FC0ED-52DB-43A2-8404-294B98E570CF}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{99D86865-B3E6-4F73-ABA4-5B9A11D75E4E}" name="#">
       <calculatedColumnFormula>K14+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9AB45042-C311-412A-950D-0BED23C880B4}" name="Score 2"/>
-    <tableColumn id="3" xr3:uid="{5467434A-5DAB-4E77-8116-1535D5C3CF2B}" name="Total Shots"/>
-    <tableColumn id="4" xr3:uid="{D2D8B880-39B0-40F7-9024-E66F7F3A18E7}" name="Accuracy (%)"/>
-    <tableColumn id="5" xr3:uid="{F88034F4-4A68-4CCB-ACF2-E74EBE57D252}" name="Headshot (%)"/>
-    <tableColumn id="6" xr3:uid="{2355B998-708B-4F48-9F00-82942B24FCBD}" name="Max Headshots in a Row"/>
-    <tableColumn id="7" xr3:uid="{9D68008E-0650-4C44-A20F-3B6C0CA43D5E}" name="Time"/>
-    <tableColumn id="8" xr3:uid="{A8DE6DD2-1EC5-41F2-BD51-57FA6F90E1AB}" name="Rating(1-100)"/>
-    <tableColumn id="9" xr3:uid="{F8E6B761-847C-4BA4-9F0A-784508357F43}" name="Immersion Rating"/>
+    <tableColumn id="2" xr3:uid="{9AB45042-C311-412A-950D-0BED23C880B4}" name="Score 2" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(L15:L32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{5467434A-5DAB-4E77-8116-1535D5C3CF2B}" name="Total Shots" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(M15:M32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{D2D8B880-39B0-40F7-9024-E66F7F3A18E7}" name="Accuracy (%)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(N15:N32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F88034F4-4A68-4CCB-ACF2-E74EBE57D252}" name="Headshot (%)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(O15:O32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{2355B998-708B-4F48-9F00-82942B24FCBD}" name="Max Headshots in a Row" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(P15:P32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{9D68008E-0650-4C44-A20F-3B6C0CA43D5E}" name="Time" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(Q15:Q32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{A8DE6DD2-1EC5-41F2-BD51-57FA6F90E1AB}" name="Rating(1-100)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(R15:R32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{F8E6B761-847C-4BA4-9F0A-784508357F43}" name="Immersion Rating" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(S15:S32)</totalsRowFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D8229619-43A8-4E4B-B48A-649A048C8BDD}" name="Table4" displayName="Table4" ref="U14:AC32" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D8229619-43A8-4E4B-B48A-649A048C8BDD}" name="Table4" displayName="Table4" ref="U14:AC33" totalsRowCount="1">
   <autoFilter ref="U14:AC32" xr:uid="{D8229619-43A8-4E4B-B48A-649A048C8BDD}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{EFBCC0BE-21CA-4481-9CAE-9FCA4803AC28}" name="#"/>
-    <tableColumn id="2" xr3:uid="{71BEEF65-25BC-4AEB-AAAA-7B56D28CBE35}" name="Score"/>
-    <tableColumn id="3" xr3:uid="{1960905F-50C6-4FA9-AABD-7D53810163E7}" name="Total Shots"/>
-    <tableColumn id="4" xr3:uid="{793FDAFD-975D-48EF-BD37-5421EBEBF7EE}" name="Accuracy (%)"/>
-    <tableColumn id="5" xr3:uid="{7ACF717A-3F03-45F7-BC43-F423C666EFD3}" name="Headshot (%)"/>
-    <tableColumn id="6" xr3:uid="{9DC2C051-99C5-4C61-AFCE-768DD3C324C8}" name="Max Headshots in a Row"/>
-    <tableColumn id="7" xr3:uid="{AADE03A1-DEB1-4B59-9C1B-2AD5B4A787C5}" name="Time"/>
-    <tableColumn id="8" xr3:uid="{BB1525E6-A6CB-48FC-A0C3-672059DE7253}" name="Rating(1-100)"/>
-    <tableColumn id="9" xr3:uid="{CB4FBB8B-FC36-426B-A500-6E01C1B68297}" name="Immersion Rating"/>
+    <tableColumn id="2" xr3:uid="{71BEEF65-25BC-4AEB-AAAA-7B56D28CBE35}" name="Score" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(V15:V32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{1960905F-50C6-4FA9-AABD-7D53810163E7}" name="Total Shots" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(W15:W32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{793FDAFD-975D-48EF-BD37-5421EBEBF7EE}" name="Accuracy (%)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(X15:X32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{7ACF717A-3F03-45F7-BC43-F423C666EFD3}" name="Headshot (%)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(Y15:Y32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{9DC2C051-99C5-4C61-AFCE-768DD3C324C8}" name="Max Headshots in a Row" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(Z15:Z32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{AADE03A1-DEB1-4B59-9C1B-2AD5B4A787C5}" name="Time" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(AA15:AA32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{BB1525E6-A6CB-48FC-A0C3-672059DE7253}" name="Rating(1-100)" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(AB15:AB32)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{CB4FBB8B-FC36-426B-A500-6E01C1B68297}" name="Immersion Rating" totalsRowFunction="custom">
+      <totalsRowFormula>AVERAGE(AC15:AC32)</totalsRowFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -622,21 +636,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF0422-255B-404C-AE6B-B5A828AC21C0}">
-  <dimension ref="A13:AC54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A13:AD54"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="24.75" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" customWidth="1"/>
-    <col min="22" max="22" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="35.625" customWidth="1"/>
+    <col min="22" max="22" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:29" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:29" ht="34.5">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -647,7 +661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -730,7 +744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29">
       <c r="A15">
         <v>1</v>
       </c>
@@ -813,7 +827,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29">
       <c r="A16">
         <f>A15+1</f>
         <v>2</v>
@@ -899,7 +913,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30">
       <c r="A17">
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
@@ -985,7 +999,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1071,149 +1085,446 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19" spans="1:30">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>1805</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>118</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>87.287999999999997</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19">
         <v>72.033000000000001</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>16</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19">
         <v>40</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19">
         <v>2050</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19">
         <v>122</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19">
         <v>88.524000000000001</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19">
         <v>88.524000000000001</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19">
         <v>20</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19">
         <v>25</v>
       </c>
-      <c r="R19" s="1">
+      <c r="R19">
         <v>95</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S19">
         <v>95</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="V19" s="1">
+      <c r="V19">
         <v>1905</v>
       </c>
-      <c r="W19" s="1">
+      <c r="W19">
         <v>109</v>
       </c>
-      <c r="X19" s="1">
+      <c r="X19">
         <v>89.908000000000001</v>
       </c>
-      <c r="Y19" s="1">
+      <c r="Y19">
         <v>89.908000000000001</v>
       </c>
-      <c r="Z19" s="1">
+      <c r="Z19">
         <v>30</v>
       </c>
-      <c r="AA19" s="1">
+      <c r="AA19">
         <v>30</v>
       </c>
-      <c r="AB19" s="1">
+      <c r="AB19">
         <v>80</v>
       </c>
-      <c r="AC19" s="1">
+      <c r="AC19">
         <v>90</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B20">
+        <v>1550</v>
+      </c>
+      <c r="C20">
+        <v>80</v>
+      </c>
+      <c r="D20">
+        <v>97.5</v>
+      </c>
+      <c r="E20">
+        <v>97.5</v>
+      </c>
+      <c r="F20">
+        <v>19</v>
+      </c>
+      <c r="G20">
+        <v>70</v>
+      </c>
+      <c r="H20">
+        <v>40</v>
+      </c>
+      <c r="I20">
+        <v>40</v>
+      </c>
       <c r="K20">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
+      <c r="L20">
+        <v>1550</v>
+      </c>
+      <c r="M20">
+        <v>83</v>
+      </c>
+      <c r="N20">
+        <v>95.18</v>
+      </c>
+      <c r="O20">
+        <v>93.97</v>
+      </c>
+      <c r="P20">
+        <v>30</v>
+      </c>
+      <c r="Q20">
+        <v>60</v>
+      </c>
+      <c r="R20">
+        <v>70</v>
+      </c>
+      <c r="S20">
+        <v>85</v>
+      </c>
       <c r="U20">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V20">
+        <v>1570</v>
+      </c>
+      <c r="W20">
+        <v>81</v>
+      </c>
+      <c r="X20">
+        <v>97.53</v>
+      </c>
+      <c r="Y20">
+        <v>97.53</v>
+      </c>
+      <c r="Z20">
+        <v>34</v>
+      </c>
+      <c r="AA20">
+        <v>90</v>
+      </c>
+      <c r="AB20">
+        <v>65</v>
+      </c>
+      <c r="AC20">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B21">
+        <v>1645</v>
+      </c>
+      <c r="C21">
+        <v>86</v>
+      </c>
+      <c r="D21">
+        <v>96.510999999999996</v>
+      </c>
+      <c r="E21">
+        <v>96.510999999999996</v>
+      </c>
+      <c r="F21">
+        <v>40</v>
+      </c>
+      <c r="G21">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>80</v>
+      </c>
+      <c r="I21">
+        <v>85</v>
+      </c>
       <c r="K21">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
+      <c r="L21">
+        <v>1940</v>
+      </c>
+      <c r="M21">
+        <v>102</v>
+      </c>
+      <c r="N21">
+        <v>96.078000000000003</v>
+      </c>
+      <c r="O21">
+        <v>96.078000000000003</v>
+      </c>
+      <c r="P21">
+        <v>41</v>
+      </c>
+      <c r="Q21">
+        <v>45</v>
+      </c>
+      <c r="R21">
+        <v>85</v>
+      </c>
+      <c r="S21">
+        <v>90</v>
+      </c>
       <c r="U21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V21">
+        <v>2015</v>
+      </c>
+      <c r="W21">
+        <v>112</v>
+      </c>
+      <c r="X21">
+        <v>91.963999999999999</v>
+      </c>
+      <c r="Y21">
+        <v>91.963999999999999</v>
+      </c>
+      <c r="Z21">
+        <v>38</v>
+      </c>
+      <c r="AA21">
+        <v>30</v>
+      </c>
+      <c r="AB21">
+        <v>90</v>
+      </c>
+      <c r="AC21">
+        <v>85</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B22">
+        <v>1835</v>
+      </c>
+      <c r="C22">
+        <v>118</v>
+      </c>
+      <c r="D22">
+        <v>82.203000000000003</v>
+      </c>
+      <c r="E22">
+        <v>82.203000000000003</v>
+      </c>
+      <c r="F22">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>45</v>
+      </c>
+      <c r="H22">
+        <v>60</v>
+      </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
       <c r="K22">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
+      <c r="L22">
+        <v>2065</v>
+      </c>
+      <c r="M22">
+        <v>130</v>
+      </c>
+      <c r="N22">
+        <v>83.846000000000004</v>
+      </c>
+      <c r="O22">
+        <v>83.075999999999993</v>
+      </c>
+      <c r="P22">
+        <v>14</v>
+      </c>
+      <c r="Q22">
+        <v>30</v>
+      </c>
+      <c r="R22">
+        <v>70</v>
+      </c>
+      <c r="S22">
+        <v>50</v>
+      </c>
       <c r="U22">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V22">
+        <v>1985</v>
+      </c>
+      <c r="W22">
+        <v>118</v>
+      </c>
+      <c r="X22">
+        <v>87.287999999999997</v>
+      </c>
+      <c r="Y22">
+        <v>87.287999999999997</v>
+      </c>
+      <c r="Z22">
+        <v>31</v>
+      </c>
+      <c r="AA22">
+        <v>30</v>
+      </c>
+      <c r="AB22">
+        <v>75</v>
+      </c>
+      <c r="AC22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B23">
+        <v>1745</v>
+      </c>
+      <c r="C23">
+        <v>89</v>
+      </c>
+      <c r="D23">
+        <v>98.876000000000005</v>
+      </c>
+      <c r="E23">
+        <v>87.572000000000003</v>
+      </c>
+      <c r="F23">
+        <v>75</v>
+      </c>
+      <c r="G23">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>60</v>
+      </c>
+      <c r="I23">
+        <v>55</v>
+      </c>
       <c r="K23">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
+      <c r="L23">
+        <v>1650</v>
+      </c>
+      <c r="M23">
+        <v>88</v>
+      </c>
+      <c r="N23">
+        <v>97.727000000000004</v>
+      </c>
+      <c r="O23">
+        <v>90.909000000000006</v>
+      </c>
+      <c r="P23">
+        <v>15</v>
+      </c>
+      <c r="Q23">
+        <v>70</v>
+      </c>
+      <c r="R23">
+        <v>75</v>
+      </c>
+      <c r="S23">
+        <v>75</v>
+      </c>
       <c r="U23">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V23">
+        <v>1785</v>
+      </c>
+      <c r="W23">
+        <v>94</v>
+      </c>
+      <c r="X23">
+        <v>96.808000000000007</v>
+      </c>
+      <c r="Y23">
+        <v>96.808000000000007</v>
+      </c>
+      <c r="Z23">
+        <v>38</v>
+      </c>
+      <c r="AA23">
+        <v>50</v>
+      </c>
+      <c r="AB23">
+        <v>65</v>
+      </c>
+      <c r="AC23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1227,7 +1538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1241,7 +1552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1255,7 +1566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1269,7 +1580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1283,7 +1594,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1297,7 +1608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1311,7 +1622,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1325,7 +1636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
@@ -1339,7 +1650,105 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29">
+      <c r="B33">
+        <f>AVERAGE(B15:B32)</f>
+        <v>1694.4444444444443</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:I33" si="3">AVERAGE(C15:C32)</f>
+        <v>95.222222222222229</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="3"/>
+        <v>92.879999999999981</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="3"/>
+        <v>89.210777777777778</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>34.888888888888886</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="3"/>
+        <v>43.888888888888886</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="3"/>
+        <v>47.777777777777779</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="3"/>
+        <v>40.666666666666664</v>
+      </c>
+      <c r="L33">
+        <f>AVERAGE(L15:L32)</f>
+        <v>1804.4444444444443</v>
+      </c>
+      <c r="M33">
+        <f>AVERAGE(M15:M32)</f>
+        <v>100.22222222222223</v>
+      </c>
+      <c r="N33">
+        <f>AVERAGE(N15:N32)</f>
+        <v>93.724555555555554</v>
+      </c>
+      <c r="O33">
+        <f t="shared" ref="M33:S33" si="4">AVERAGE(O15:O32)</f>
+        <v>91.197666666666663</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="4"/>
+        <v>26.777777777777779</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="4"/>
+        <v>45.555555555555557</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="4"/>
+        <v>67.444444444444443</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="4"/>
+        <v>71.111111111111114</v>
+      </c>
+      <c r="V33">
+        <f>AVERAGE(V15:V32)</f>
+        <v>1822.7777777777778</v>
+      </c>
+      <c r="W33">
+        <f t="shared" ref="W33:AC33" si="5">AVERAGE(W15:W32)</f>
+        <v>100.88888888888889</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="5"/>
+        <v>93.119111111111124</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="5"/>
+        <v>92.123888888888885</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="5"/>
+        <v>30.777777777777779</v>
+      </c>
+      <c r="AA33">
+        <f t="shared" si="5"/>
+        <v>43.888888888888886</v>
+      </c>
+      <c r="AB33">
+        <f t="shared" si="5"/>
+        <v>71.666666666666671</v>
+      </c>
+      <c r="AC33">
+        <f t="shared" si="5"/>
+        <v>68.888888888888886</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -1347,7 +1756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29">
       <c r="B37" s="3">
         <v>1</v>
       </c>
@@ -1364,7 +1773,7 @@
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29">
       <c r="B38" s="3">
         <f>B37+1</f>
         <v>2</v>
@@ -1382,9 +1791,9 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29">
       <c r="B39" s="3">
-        <f t="shared" ref="B39:B54" si="3">B38+1</f>
+        <f t="shared" ref="B39:B54" si="6">B38+1</f>
         <v>3</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -1400,9 +1809,9 @@
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29">
       <c r="B40" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -1418,9 +1827,9 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29">
       <c r="B41" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -1436,72 +1845,84 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="1">
-        <f t="shared" si="3"/>
+    <row r="42" spans="2:29">
+      <c r="B42" s="3">
+        <f>B41+1</f>
         <v>6</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="C42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="1">
-        <f t="shared" si="3"/>
+      <c r="F42">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29">
+      <c r="B43" s="3">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="1">
-        <f t="shared" si="3"/>
+      <c r="D43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29">
+      <c r="B44" s="3">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="1">
-        <f t="shared" si="3"/>
+      <c r="D44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>0.28100000000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29">
+      <c r="B45" s="3">
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="C45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="1">
-        <f t="shared" si="3"/>
+      <c r="E45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>0.54600000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29">
+      <c r="B46" s="5">
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -1511,9 +1932,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29">
       <c r="B47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -1526,9 +1947,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29">
       <c r="B48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -1541,9 +1962,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5">
       <c r="B49" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -1556,9 +1977,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5">
       <c r="B50" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -1571,9 +1992,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5">
       <c r="B51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -1586,9 +2007,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5">
       <c r="B52" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -1601,9 +2022,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5">
       <c r="B53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -1616,9 +2037,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5">
       <c r="B54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="C54" s="1" t="s">

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6503BBBA-8B88-4E8A-B810-ACE076FEE94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428D2561-BBE3-43FA-A446-F5FBB31B29B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
   <si>
     <t>None</t>
   </si>
@@ -105,13 +105,19 @@
   </si>
   <si>
     <t xml:space="preserve">I found the music fun but could sense it took me out of the game a little bit due to the "fantasy feel", but could see it working in other settings more. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">For me personally I think the 1st Test(Sampled) felt very long because I couldn’t fully expect it all. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found the music satisfying, Helped feel immersed. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,20 +643,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF0422-255B-404C-AE6B-B5A828AC21C0}">
   <dimension ref="A13:AD54"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.375" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="24.75" customWidth="1"/>
-    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="35.625" customWidth="1"/>
-    <col min="22" max="22" width="10.375" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" customWidth="1"/>
+    <col min="22" max="22" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:29" ht="34.5">
+    <row r="13" spans="1:29" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -661,7 +667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -744,7 +750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
@@ -827,7 +833,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>A15+1</f>
         <v>2</v>
@@ -913,7 +919,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
@@ -999,7 +1005,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1085,7 +1091,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:30">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1174,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1263,7 +1269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:30">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1352,7 +1358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:30">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1438,7 +1444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:30">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1524,21 +1530,96 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:30">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="B24">
+        <v>1760</v>
+      </c>
+      <c r="C24">
+        <v>98</v>
+      </c>
+      <c r="D24">
+        <v>91.835999999999999</v>
+      </c>
+      <c r="E24">
+        <v>91.835999999999999</v>
+      </c>
+      <c r="F24">
+        <v>25</v>
+      </c>
+      <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="H24">
+        <v>80</v>
+      </c>
+      <c r="I24">
+        <v>95</v>
+      </c>
       <c r="K24">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
+      <c r="L24">
+        <v>1460</v>
+      </c>
+      <c r="M24">
+        <v>95</v>
+      </c>
+      <c r="N24">
+        <v>85.263000000000005</v>
+      </c>
+      <c r="O24">
+        <v>75.789000000000001</v>
+      </c>
+      <c r="P24">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>120</v>
+      </c>
+      <c r="R24">
+        <v>70</v>
+      </c>
+      <c r="S24">
+        <v>90</v>
+      </c>
       <c r="U24">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:30">
+      <c r="V24">
+        <v>1685</v>
+      </c>
+      <c r="W24">
+        <v>104</v>
+      </c>
+      <c r="X24">
+        <v>85.575999999999993</v>
+      </c>
+      <c r="Y24">
+        <v>83.653000000000006</v>
+      </c>
+      <c r="Z24">
+        <v>25</v>
+      </c>
+      <c r="AA24">
+        <v>60</v>
+      </c>
+      <c r="AB24">
+        <v>70</v>
+      </c>
+      <c r="AC24">
+        <v>80</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1551,8 +1632,11 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:30">
+      <c r="AD25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1566,7 +1650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:30">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1580,7 +1664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:30">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1594,7 +1678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:30">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1608,7 +1692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:30">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1622,7 +1706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:30">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1636,7 +1720,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:30">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
@@ -1650,105 +1734,105 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>AVERAGE(B15:B32)</f>
-        <v>1694.4444444444443</v>
+        <v>1701</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:I33" si="3">AVERAGE(C15:C32)</f>
-        <v>95.222222222222229</v>
+        <v>95.5</v>
       </c>
       <c r="D33">
         <f t="shared" si="3"/>
-        <v>92.879999999999981</v>
+        <v>92.775599999999983</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>89.210777777777778</v>
+        <v>89.473300000000009</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>34.888888888888886</v>
+        <v>33.9</v>
       </c>
       <c r="G33">
         <f t="shared" si="3"/>
-        <v>43.888888888888886</v>
+        <v>45.5</v>
       </c>
       <c r="H33">
         <f t="shared" si="3"/>
-        <v>47.777777777777779</v>
+        <v>51</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
-        <v>40.666666666666664</v>
+        <v>46.1</v>
       </c>
       <c r="L33">
         <f>AVERAGE(L15:L32)</f>
-        <v>1804.4444444444443</v>
+        <v>1770</v>
       </c>
       <c r="M33">
         <f>AVERAGE(M15:M32)</f>
-        <v>100.22222222222223</v>
+        <v>99.7</v>
       </c>
       <c r="N33">
         <f>AVERAGE(N15:N32)</f>
-        <v>93.724555555555554</v>
+        <v>92.878399999999999</v>
       </c>
       <c r="O33">
-        <f t="shared" ref="M33:S33" si="4">AVERAGE(O15:O32)</f>
-        <v>91.197666666666663</v>
+        <f t="shared" ref="O33:S33" si="4">AVERAGE(O15:O32)</f>
+        <v>89.656800000000004</v>
       </c>
       <c r="P33">
         <f t="shared" si="4"/>
-        <v>26.777777777777779</v>
+        <v>26.1</v>
       </c>
       <c r="Q33">
         <f t="shared" si="4"/>
-        <v>45.555555555555557</v>
+        <v>53</v>
       </c>
       <c r="R33">
         <f t="shared" si="4"/>
-        <v>67.444444444444443</v>
+        <v>67.7</v>
       </c>
       <c r="S33">
         <f t="shared" si="4"/>
-        <v>71.111111111111114</v>
+        <v>73</v>
       </c>
       <c r="V33">
         <f>AVERAGE(V15:V32)</f>
-        <v>1822.7777777777778</v>
+        <v>1809</v>
       </c>
       <c r="W33">
         <f t="shared" ref="W33:AC33" si="5">AVERAGE(W15:W32)</f>
-        <v>100.88888888888889</v>
+        <v>101.2</v>
       </c>
       <c r="X33">
         <f t="shared" si="5"/>
-        <v>93.119111111111124</v>
+        <v>92.364800000000017</v>
       </c>
       <c r="Y33">
         <f t="shared" si="5"/>
-        <v>92.123888888888885</v>
+        <v>91.276800000000009</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>30.777777777777779</v>
+        <v>30.2</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>43.888888888888886</v>
+        <v>45.5</v>
       </c>
       <c r="AB33">
         <f t="shared" si="5"/>
-        <v>71.666666666666671</v>
+        <v>71.5</v>
       </c>
       <c r="AC33">
         <f t="shared" si="5"/>
-        <v>68.888888888888886</v>
-      </c>
-    </row>
-    <row r="36" spans="2:29">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -1756,7 +1840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
         <v>1</v>
       </c>
@@ -1773,7 +1857,7 @@
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <f>B37+1</f>
         <v>2</v>
@@ -1791,7 +1875,7 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
         <f t="shared" ref="B39:B54" si="6">B38+1</f>
         <v>3</v>
@@ -1809,7 +1893,7 @@
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -1827,7 +1911,7 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -1845,7 +1929,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
         <f>B41+1</f>
         <v>6</v>
@@ -1863,7 +1947,7 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -1881,7 +1965,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -1899,7 +1983,7 @@
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -1917,27 +2001,30 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
-      <c r="B46" s="5">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B46" s="3">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="C46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29">
-      <c r="B47" s="1">
+      <c r="F46">
+        <v>0.44500000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -1947,7 +2034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -1962,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -1977,7 +2064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="1">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -1992,7 +2079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="1">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -2007,7 +2094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -2022,7 +2109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -2037,7 +2124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <f t="shared" si="6"/>
         <v>18</v>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428D2561-BBE3-43FA-A446-F5FBB31B29B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0E8FA7-543C-4D2A-B69F-BD310BE2EB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,15 +146,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,11 +164,6 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -186,24 +174,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
-    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -642,21 +627,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF0422-255B-404C-AE6B-B5A828AC21C0}">
-  <dimension ref="A13:AD54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A13:AD55"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="3" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="24.75" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="35.5703125" customWidth="1"/>
-    <col min="22" max="22" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="35.625" customWidth="1"/>
+    <col min="22" max="22" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:29" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:29" ht="36">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -667,7 +652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -750,7 +735,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29">
       <c r="A15">
         <v>1</v>
       </c>
@@ -833,7 +818,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29">
       <c r="A16">
         <f>A15+1</f>
         <v>2</v>
@@ -919,7 +904,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30">
       <c r="A17">
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
@@ -1005,7 +990,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1091,7 +1076,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1180,7 +1165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1269,7 +1254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1358,7 +1343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1444,7 +1429,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1530,7 +1515,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1619,24 +1604,96 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B25">
+        <v>1600</v>
+      </c>
+      <c r="C25">
+        <v>80</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25">
+        <v>30</v>
+      </c>
+      <c r="H25">
+        <v>22</v>
+      </c>
+      <c r="I25">
+        <v>30</v>
+      </c>
       <c r="K25">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
+      <c r="L25">
+        <v>1735</v>
+      </c>
+      <c r="M25">
+        <v>88</v>
+      </c>
+      <c r="N25">
+        <v>98.863</v>
+      </c>
+      <c r="O25">
+        <v>98.863</v>
+      </c>
+      <c r="P25">
+        <v>84</v>
+      </c>
+      <c r="Q25">
+        <v>30</v>
+      </c>
+      <c r="R25">
+        <v>30</v>
+      </c>
+      <c r="S25">
+        <v>45</v>
+      </c>
       <c r="U25">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
+      <c r="V25">
+        <v>1665</v>
+      </c>
+      <c r="W25">
+        <v>87</v>
+      </c>
+      <c r="X25">
+        <v>96.551000000000002</v>
+      </c>
+      <c r="Y25">
+        <v>96.551000000000002</v>
+      </c>
+      <c r="Z25">
+        <v>49</v>
+      </c>
+      <c r="AA25">
+        <v>40</v>
+      </c>
+      <c r="AB25">
+        <v>45</v>
+      </c>
+      <c r="AC25">
+        <v>80</v>
+      </c>
       <c r="AD25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1650,7 +1707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1664,7 +1721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1678,7 +1735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1692,7 +1749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1706,7 +1763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1720,7 +1777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
@@ -1734,105 +1791,105 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29">
       <c r="B33">
         <f>AVERAGE(B15:B32)</f>
-        <v>1701</v>
+        <v>1691.8181818181818</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:I33" si="3">AVERAGE(C15:C32)</f>
-        <v>95.5</v>
+        <v>94.090909090909093</v>
       </c>
       <c r="D33">
         <f t="shared" si="3"/>
-        <v>92.775599999999983</v>
+        <v>93.432363636363618</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>89.473300000000009</v>
+        <v>90.430272727272737</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>33.9</v>
+        <v>38.090909090909093</v>
       </c>
       <c r="G33">
         <f t="shared" si="3"/>
-        <v>45.5</v>
+        <v>44.090909090909093</v>
       </c>
       <c r="H33">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>48.363636363636367</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
-        <v>46.1</v>
+        <v>44.636363636363633</v>
       </c>
       <c r="L33">
         <f>AVERAGE(L15:L32)</f>
-        <v>1770</v>
+        <v>1766.8181818181818</v>
       </c>
       <c r="M33">
         <f>AVERAGE(M15:M32)</f>
-        <v>99.7</v>
+        <v>98.63636363636364</v>
       </c>
       <c r="N33">
         <f>AVERAGE(N15:N32)</f>
-        <v>92.878399999999999</v>
+        <v>93.422454545454542</v>
       </c>
       <c r="O33">
         <f t="shared" ref="O33:S33" si="4">AVERAGE(O15:O32)</f>
-        <v>89.656800000000004</v>
+        <v>90.49372727272727</v>
       </c>
       <c r="P33">
         <f t="shared" si="4"/>
-        <v>26.1</v>
+        <v>31.363636363636363</v>
       </c>
       <c r="Q33">
         <f t="shared" si="4"/>
-        <v>53</v>
+        <v>50.909090909090907</v>
       </c>
       <c r="R33">
         <f t="shared" si="4"/>
-        <v>67.7</v>
+        <v>64.272727272727266</v>
       </c>
       <c r="S33">
         <f t="shared" si="4"/>
-        <v>73</v>
+        <v>70.454545454545453</v>
       </c>
       <c r="V33">
         <f>AVERAGE(V15:V32)</f>
-        <v>1809</v>
+        <v>1795.909090909091</v>
       </c>
       <c r="W33">
         <f t="shared" ref="W33:AC33" si="5">AVERAGE(W15:W32)</f>
-        <v>101.2</v>
+        <v>99.909090909090907</v>
       </c>
       <c r="X33">
         <f t="shared" si="5"/>
-        <v>92.364800000000017</v>
+        <v>92.745363636363649</v>
       </c>
       <c r="Y33">
         <f t="shared" si="5"/>
-        <v>91.276800000000009</v>
+        <v>91.75627272727273</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>30.2</v>
+        <v>31.90909090909091</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="AB33">
         <f t="shared" si="5"/>
-        <v>71.5</v>
+        <v>69.090909090909093</v>
       </c>
       <c r="AC33">
         <f t="shared" si="5"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+        <v>70.909090909090907</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -1840,7 +1897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:29">
       <c r="B37" s="3">
         <v>1</v>
       </c>
@@ -1857,7 +1914,7 @@
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:29">
       <c r="B38" s="3">
         <f>B37+1</f>
         <v>2</v>
@@ -1875,7 +1932,7 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:29">
       <c r="B39" s="3">
         <f t="shared" ref="B39:B54" si="6">B38+1</f>
         <v>3</v>
@@ -1893,7 +1950,7 @@
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29">
       <c r="B40" s="3">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -1911,7 +1968,7 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:29">
       <c r="B41" s="3">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -1929,7 +1986,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29">
       <c r="B42" s="3">
         <f>B41+1</f>
         <v>6</v>
@@ -1947,7 +2004,7 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29">
       <c r="B43" s="3">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -1965,7 +2022,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29">
       <c r="B44" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -1983,7 +2040,7 @@
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:29">
       <c r="B45" s="3">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -2001,7 +2058,7 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:29">
       <c r="B46" s="3">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -2019,22 +2076,25 @@
         <v>0.44500000000000001</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B47" s="5">
+    <row r="47" spans="2:29">
+      <c r="B47" s="3">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29">
       <c r="B48" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -2049,7 +2109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6">
       <c r="B49" s="1">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -2064,7 +2124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6">
       <c r="B50" s="1">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -2079,7 +2139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6">
       <c r="B51" s="1">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -2094,7 +2154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6">
       <c r="B52" s="1">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -2109,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6">
       <c r="B53" s="1">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -2124,7 +2184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6">
       <c r="B54" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -2137,6 +2197,12 @@
       </c>
       <c r="E54" s="1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="F55">
+        <f>AVERAGE(F37:F54)</f>
+        <v>0.4675454545454546</v>
       </c>
     </row>
   </sheetData>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0E8FA7-543C-4D2A-B69F-BD310BE2EB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759A2B55-AF49-4D95-983C-D234ADFF2F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="28">
   <si>
     <t>None</t>
   </si>
@@ -111,13 +111,22 @@
   </si>
   <si>
     <t xml:space="preserve">Found the music satisfying, Helped feel immersed. </t>
+  </si>
+  <si>
+    <t>Sometime concentrate more no sound, mainly because its not a full game with movement. Music felt better than sampled, felt progressive and rewarding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loves aim trainers but this type - hence the low ratings. Felt distraced on last test after knowing that I was going to ask them about time. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like the musical shots. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,20 +637,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FF0422-255B-404C-AE6B-B5A828AC21C0}">
   <dimension ref="A13:AD55"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.375" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="24.75" customWidth="1"/>
-    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="35.625" customWidth="1"/>
-    <col min="22" max="22" width="10.375" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" customWidth="1"/>
+    <col min="22" max="22" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:29" ht="36">
+    <row r="13" spans="1:29" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -652,7 +661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -735,7 +744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
@@ -818,7 +827,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>A15+1</f>
         <v>2</v>
@@ -904,7 +913,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" ref="A17:A31" si="0">A16+1</f>
         <v>3</v>
@@ -990,7 +999,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1076,7 +1085,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:30">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1165,7 +1174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1254,7 +1263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:30">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1343,7 +1352,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:30">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1429,7 +1438,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:30">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1515,7 +1524,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:30">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1604,7 +1613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:30">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1693,63 +1702,360 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:30">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B26">
+        <v>1600</v>
+      </c>
+      <c r="C26">
+        <v>90</v>
+      </c>
+      <c r="D26">
+        <v>91.111000000000004</v>
+      </c>
+      <c r="E26">
+        <v>91.111000000000004</v>
+      </c>
+      <c r="F26">
+        <v>29</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26">
+        <v>50</v>
+      </c>
+      <c r="I26">
+        <v>60</v>
+      </c>
       <c r="K26">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
+      <c r="L26">
+        <v>1450</v>
+      </c>
+      <c r="M26">
+        <v>78</v>
+      </c>
+      <c r="N26">
+        <v>94.870999999999995</v>
+      </c>
+      <c r="O26">
+        <v>93.588999999999999</v>
+      </c>
+      <c r="P26">
+        <v>15</v>
+      </c>
+      <c r="Q26">
+        <v>20</v>
+      </c>
+      <c r="R26">
+        <v>60</v>
+      </c>
+      <c r="S26">
+        <v>60</v>
+      </c>
       <c r="U26">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:30">
+      <c r="V26">
+        <v>1500</v>
+      </c>
+      <c r="W26">
+        <v>88</v>
+      </c>
+      <c r="X26">
+        <v>88.635999999999996</v>
+      </c>
+      <c r="Y26">
+        <v>87.5</v>
+      </c>
+      <c r="Z26">
+        <v>19</v>
+      </c>
+      <c r="AA26">
+        <v>30</v>
+      </c>
+      <c r="AB26">
+        <v>70</v>
+      </c>
+      <c r="AC26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B27">
+        <v>1495</v>
+      </c>
+      <c r="C27">
+        <v>76</v>
+      </c>
+      <c r="D27">
+        <v>98.683999999999997</v>
+      </c>
+      <c r="E27">
+        <v>98.683999999999997</v>
+      </c>
+      <c r="F27">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>120</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>55</v>
+      </c>
       <c r="K27">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
+      <c r="L27">
+        <v>1360</v>
+      </c>
+      <c r="M27">
+        <v>73</v>
+      </c>
+      <c r="N27">
+        <v>94.52</v>
+      </c>
+      <c r="O27">
+        <v>94.52</v>
+      </c>
+      <c r="P27">
+        <v>32</v>
+      </c>
+      <c r="Q27">
+        <v>60</v>
+      </c>
+      <c r="R27">
+        <v>25</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
       <c r="U27">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:30">
+      <c r="V27">
+        <v>1775</v>
+      </c>
+      <c r="W27">
+        <v>95</v>
+      </c>
+      <c r="X27">
+        <v>94.736000000000004</v>
+      </c>
+      <c r="Y27">
+        <v>94.376000000000005</v>
+      </c>
+      <c r="Z27">
+        <v>30</v>
+      </c>
+      <c r="AA27">
+        <v>60</v>
+      </c>
+      <c r="AB27">
+        <v>35</v>
+      </c>
+      <c r="AC27">
+        <v>55</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
+      <c r="B28">
+        <v>2265</v>
+      </c>
+      <c r="C28">
+        <v>122</v>
+      </c>
+      <c r="D28">
+        <v>94.262</v>
+      </c>
+      <c r="E28">
+        <v>94.262</v>
+      </c>
+      <c r="F28">
+        <v>26</v>
+      </c>
+      <c r="G28">
+        <v>90</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>100</v>
+      </c>
       <c r="K28">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
+      <c r="L28">
+        <v>2365</v>
+      </c>
+      <c r="M28">
+        <v>132</v>
+      </c>
+      <c r="N28">
+        <v>91.665999999999997</v>
+      </c>
+      <c r="O28">
+        <v>91.665999999999997</v>
+      </c>
+      <c r="P28">
+        <v>26</v>
+      </c>
+      <c r="Q28">
+        <v>60</v>
+      </c>
+      <c r="R28">
+        <v>5</v>
+      </c>
+      <c r="S28">
+        <v>70</v>
+      </c>
       <c r="U28">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:30">
+      <c r="V28">
+        <v>2165</v>
+      </c>
+      <c r="W28">
+        <v>127</v>
+      </c>
+      <c r="X28">
+        <v>88.188000000000002</v>
+      </c>
+      <c r="Y28">
+        <v>88.188000000000002</v>
+      </c>
+      <c r="Z28">
+        <v>31</v>
+      </c>
+      <c r="AA28">
+        <v>60</v>
+      </c>
+      <c r="AB28">
+        <v>5</v>
+      </c>
+      <c r="AC28">
+        <v>80</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
+      <c r="B29">
+        <v>1700</v>
+      </c>
+      <c r="C29">
+        <v>118</v>
+      </c>
+      <c r="D29">
+        <v>77.965999999999994</v>
+      </c>
+      <c r="E29">
+        <v>77.117999999999995</v>
+      </c>
+      <c r="F29">
+        <v>9</v>
+      </c>
+      <c r="G29">
+        <v>60</v>
+      </c>
+      <c r="H29">
+        <v>50</v>
+      </c>
+      <c r="I29">
+        <v>46</v>
+      </c>
       <c r="K29">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
+      <c r="L29">
+        <v>1395</v>
+      </c>
+      <c r="M29">
+        <v>89</v>
+      </c>
+      <c r="N29">
+        <v>83.146000000000001</v>
+      </c>
+      <c r="O29">
+        <v>82.022000000000006</v>
+      </c>
+      <c r="P29">
+        <v>10</v>
+      </c>
+      <c r="Q29">
+        <v>45</v>
+      </c>
+      <c r="R29">
+        <v>68</v>
+      </c>
+      <c r="S29">
+        <v>75</v>
+      </c>
       <c r="U29">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:30">
+      <c r="V29">
+        <v>1750</v>
+      </c>
+      <c r="W29">
+        <v>113</v>
+      </c>
+      <c r="X29">
+        <v>82.3</v>
+      </c>
+      <c r="Y29">
+        <v>81.415000000000006</v>
+      </c>
+      <c r="Z29">
+        <v>21</v>
+      </c>
+      <c r="AA29">
+        <v>55</v>
+      </c>
+      <c r="AB29">
+        <v>74</v>
+      </c>
+      <c r="AC29">
+        <v>75</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1763,7 +2069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:30">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1777,7 +2083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:30">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
@@ -1791,105 +2097,105 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:29">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>AVERAGE(B15:B32)</f>
-        <v>1691.8181818181818</v>
+        <v>1711.3333333333333</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:I33" si="3">AVERAGE(C15:C32)</f>
-        <v>94.090909090909093</v>
+        <v>96.066666666666663</v>
       </c>
       <c r="D33">
         <f t="shared" si="3"/>
-        <v>93.432363636363618</v>
+        <v>92.651933333333318</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>90.430272727272737</v>
+        <v>90.393866666666653</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>38.090909090909093</v>
+        <v>35.93333333333333</v>
       </c>
       <c r="G33">
         <f t="shared" si="3"/>
-        <v>44.090909090909093</v>
+        <v>52</v>
       </c>
       <c r="H33">
         <f t="shared" si="3"/>
-        <v>48.363636363636367</v>
+        <v>44.2</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
-        <v>44.636363636363633</v>
+        <v>50.133333333333333</v>
       </c>
       <c r="L33">
         <f>AVERAGE(L15:L32)</f>
-        <v>1766.8181818181818</v>
+        <v>1733.6666666666667</v>
       </c>
       <c r="M33">
         <f>AVERAGE(M15:M32)</f>
-        <v>98.63636363636364</v>
+        <v>97.13333333333334</v>
       </c>
       <c r="N33">
         <f>AVERAGE(N15:N32)</f>
-        <v>93.422454545454542</v>
+        <v>92.789999999999992</v>
       </c>
       <c r="O33">
         <f t="shared" ref="O33:S33" si="4">AVERAGE(O15:O32)</f>
-        <v>90.49372727272727</v>
+        <v>90.481866666666662</v>
       </c>
       <c r="P33">
         <f t="shared" si="4"/>
-        <v>31.363636363636363</v>
+        <v>28.533333333333335</v>
       </c>
       <c r="Q33">
         <f t="shared" si="4"/>
-        <v>50.909090909090907</v>
+        <v>49.666666666666664</v>
       </c>
       <c r="R33">
         <f t="shared" si="4"/>
-        <v>64.272727272727266</v>
+        <v>57.666666666666664</v>
       </c>
       <c r="S33">
         <f t="shared" si="4"/>
-        <v>70.454545454545453</v>
+        <v>68.666666666666671</v>
       </c>
       <c r="V33">
         <f>AVERAGE(V15:V32)</f>
-        <v>1795.909090909091</v>
+        <v>1796.3333333333333</v>
       </c>
       <c r="W33">
         <f t="shared" ref="W33:AC33" si="5">AVERAGE(W15:W32)</f>
-        <v>99.909090909090907</v>
+        <v>101.46666666666667</v>
       </c>
       <c r="X33">
         <f t="shared" si="5"/>
-        <v>92.745363636363649</v>
+        <v>91.603933333333359</v>
       </c>
       <c r="Y33">
         <f t="shared" si="5"/>
-        <v>91.75627272727273</v>
+        <v>90.719866666666661</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>31.90909090909091</v>
+        <v>30.133333333333333</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="AB33">
         <f t="shared" si="5"/>
-        <v>69.090909090909093</v>
+        <v>62.93333333333333</v>
       </c>
       <c r="AC33">
         <f t="shared" si="5"/>
-        <v>70.909090909090907</v>
-      </c>
-    </row>
-    <row r="36" spans="2:29">
+        <v>71.333333333333329</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -1897,7 +2203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:29">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
         <v>1</v>
       </c>
@@ -1914,7 +2220,7 @@
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="38" spans="2:29">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <f>B37+1</f>
         <v>2</v>
@@ -1932,7 +2238,7 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="39" spans="2:29">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
         <f t="shared" ref="B39:B54" si="6">B38+1</f>
         <v>3</v>
@@ -1950,7 +2256,7 @@
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:29">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -1968,7 +2274,7 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:29">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -1986,7 +2292,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:29">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
         <f>B41+1</f>
         <v>6</v>
@@ -2004,7 +2310,7 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="43" spans="2:29">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -2022,7 +2328,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="44" spans="2:29">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -2040,7 +2346,7 @@
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="45" spans="2:29">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -2058,7 +2364,7 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="46" spans="2:29">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="3">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -2076,7 +2382,7 @@
         <v>0.44500000000000001</v>
       </c>
     </row>
-    <row r="47" spans="2:29">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -2094,67 +2400,79 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="48" spans="2:29">
-      <c r="B48" s="1">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B48" s="3">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1">
+      <c r="F48">
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="3">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="1">
+      <c r="F49">
+        <v>0.40600000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="3">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="1">
+      <c r="F50">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="3">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="F51">
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -2169,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -2184,7 +2502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -2199,10 +2517,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F55">
         <f>AVERAGE(F37:F54)</f>
-        <v>0.4675454545454546</v>
+        <v>0.44400000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759A2B55-AF49-4D95-983C-D234ADFF2F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B6C62A-9452-451D-90E5-C0AE97CB4027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="30">
   <si>
     <t>None</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t xml:space="preserve">Like the musical shots. </t>
+  </si>
+  <si>
+    <t>2??</t>
+  </si>
+  <si>
+    <t>0???</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1578,7 @@
       <c r="P24">
         <v>20</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24">
         <v>120</v>
       </c>
       <c r="R24">
@@ -2060,13 +2066,85 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
+      <c r="B30">
+        <v>1420</v>
+      </c>
+      <c r="C30">
+        <v>71</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <v>71</v>
+      </c>
+      <c r="G30">
+        <v>80</v>
+      </c>
+      <c r="H30">
+        <v>55</v>
+      </c>
+      <c r="I30">
+        <v>30</v>
+      </c>
       <c r="K30">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
+      <c r="L30">
+        <v>1355</v>
+      </c>
+      <c r="M30">
+        <v>69</v>
+      </c>
+      <c r="N30">
+        <v>98.55</v>
+      </c>
+      <c r="O30">
+        <v>98.55</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q30">
+        <v>30</v>
+      </c>
+      <c r="R30">
+        <v>70</v>
+      </c>
+      <c r="S30">
+        <v>50</v>
+      </c>
       <c r="U30">
         <f t="shared" si="2"/>
         <v>16</v>
+      </c>
+      <c r="V30">
+        <v>1520</v>
+      </c>
+      <c r="W30">
+        <v>76</v>
+      </c>
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>100</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA30">
+        <v>60</v>
+      </c>
+      <c r="AB30">
+        <v>75</v>
+      </c>
+      <c r="AC30">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -2074,13 +2152,85 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
+      <c r="B31">
+        <v>1470</v>
+      </c>
+      <c r="C31">
+        <v>76</v>
+      </c>
+      <c r="D31">
+        <v>97.367999999999995</v>
+      </c>
+      <c r="E31">
+        <v>97.367999999999995</v>
+      </c>
+      <c r="F31">
+        <v>57</v>
+      </c>
+      <c r="G31">
+        <v>30</v>
+      </c>
+      <c r="H31">
+        <v>50</v>
+      </c>
+      <c r="I31">
+        <v>90</v>
+      </c>
       <c r="K31">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
+      <c r="L31">
+        <v>1515</v>
+      </c>
+      <c r="M31">
+        <v>77</v>
+      </c>
+      <c r="N31">
+        <v>98.700999999999993</v>
+      </c>
+      <c r="O31">
+        <v>98.700999999999993</v>
+      </c>
+      <c r="P31">
+        <v>46</v>
+      </c>
+      <c r="Q31">
+        <v>40</v>
+      </c>
+      <c r="R31">
+        <v>80</v>
+      </c>
+      <c r="S31">
+        <v>95</v>
+      </c>
       <c r="U31">
         <f t="shared" si="2"/>
         <v>17</v>
+      </c>
+      <c r="V31">
+        <v>1510</v>
+      </c>
+      <c r="W31">
+        <v>78</v>
+      </c>
+      <c r="X31">
+        <v>97.435000000000002</v>
+      </c>
+      <c r="Y31">
+        <v>97.435000000000002</v>
+      </c>
+      <c r="Z31">
+        <v>48</v>
+      </c>
+      <c r="AA31">
+        <v>45</v>
+      </c>
+      <c r="AB31">
+        <v>70</v>
+      </c>
+      <c r="AC31">
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -2100,99 +2250,99 @@
     <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>AVERAGE(B15:B32)</f>
-        <v>1711.3333333333333</v>
+        <v>1680</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:I33" si="3">AVERAGE(C15:C32)</f>
-        <v>96.066666666666663</v>
+        <v>93.411764705882348</v>
       </c>
       <c r="D33">
         <f t="shared" si="3"/>
-        <v>92.651933333333318</v>
+        <v>93.361588235294107</v>
       </c>
       <c r="E33">
         <f t="shared" si="3"/>
-        <v>90.393866666666653</v>
+        <v>91.369176470588229</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>35.93333333333333</v>
+        <v>39.235294117647058</v>
       </c>
       <c r="G33">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>52.352941176470587</v>
       </c>
       <c r="H33">
         <f t="shared" si="3"/>
-        <v>44.2</v>
+        <v>45.176470588235297</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
-        <v>50.133333333333333</v>
+        <v>51.294117647058826</v>
       </c>
       <c r="L33">
         <f>AVERAGE(L15:L32)</f>
-        <v>1733.6666666666667</v>
+        <v>1698.5294117647059</v>
       </c>
       <c r="M33">
         <f>AVERAGE(M15:M32)</f>
-        <v>97.13333333333334</v>
+        <v>94.294117647058826</v>
       </c>
       <c r="N33">
         <f>AVERAGE(N15:N32)</f>
-        <v>92.789999999999992</v>
+        <v>93.476529411764702</v>
       </c>
       <c r="O33">
         <f t="shared" ref="O33:S33" si="4">AVERAGE(O15:O32)</f>
-        <v>90.481866666666662</v>
+        <v>91.439941176470583</v>
       </c>
       <c r="P33">
         <f t="shared" si="4"/>
-        <v>28.533333333333335</v>
+        <v>29.625</v>
       </c>
       <c r="Q33">
         <f t="shared" si="4"/>
-        <v>49.666666666666664</v>
+        <v>47.941176470588232</v>
       </c>
       <c r="R33">
         <f t="shared" si="4"/>
-        <v>57.666666666666664</v>
+        <v>59.705882352941174</v>
       </c>
       <c r="S33">
         <f t="shared" si="4"/>
-        <v>68.666666666666671</v>
+        <v>69.117647058823536</v>
       </c>
       <c r="V33">
         <f>AVERAGE(V15:V32)</f>
-        <v>1796.3333333333333</v>
+        <v>1763.2352941176471</v>
       </c>
       <c r="W33">
         <f t="shared" ref="W33:AC33" si="5">AVERAGE(W15:W32)</f>
-        <v>101.46666666666667</v>
+        <v>98.588235294117652</v>
       </c>
       <c r="X33">
         <f t="shared" si="5"/>
-        <v>91.603933333333359</v>
+        <v>92.440823529411787</v>
       </c>
       <c r="Y33">
         <f t="shared" si="5"/>
-        <v>90.719866666666661</v>
+        <v>91.660764705882343</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>30.133333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>46.666666666666664</v>
+        <v>47.352941176470587</v>
       </c>
       <c r="AB33">
         <f t="shared" si="5"/>
-        <v>62.93333333333333</v>
+        <v>64.058823529411768</v>
       </c>
       <c r="AC33">
         <f t="shared" si="5"/>
-        <v>71.333333333333329</v>
+        <v>71.470588235294116</v>
       </c>
     </row>
     <row r="36" spans="2:29" x14ac:dyDescent="0.25">
@@ -2473,33 +2623,39 @@
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="1">
+      <c r="B52" s="3">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="F52">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="1">
+      <c r="B53" s="3">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="3" t="s">
         <v>1</v>
+      </c>
+      <c r="F53">
+        <v>0.625</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
@@ -2520,7 +2676,7 @@
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F55">
         <f>AVERAGE(F37:F54)</f>
-        <v>0.44400000000000001</v>
+        <v>0.47264705882352942</v>
       </c>
     </row>
   </sheetData>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U2260777\Downloads\DisertationWork\Other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B6C62A-9452-451D-90E5-C0AE97CB4027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122A457-1882-4A65-B748-A9511CB78AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="31">
   <si>
     <t>None</t>
   </si>
@@ -122,10 +122,13 @@
     <t xml:space="preserve">Like the musical shots. </t>
   </si>
   <si>
-    <t>2??</t>
-  </si>
-  <si>
-    <t>0???</t>
+    <t>The headshot is satisfying in sound and the music is exciting</t>
+  </si>
+  <si>
+    <t>I think I did better on the none sound (Later stated most likely sue to no feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I liked both the music one and none music, but could concentrate slightly more without it, feeling more enjoyable with just normal sounds. </t>
   </si>
 </sst>
 </file>
@@ -2106,8 +2109,8 @@
       <c r="O30">
         <v>98.55</v>
       </c>
-      <c r="P30" s="1" t="s">
-        <v>28</v>
+      <c r="P30" s="1">
+        <v>2</v>
       </c>
       <c r="Q30">
         <v>30</v>
@@ -2134,8 +2137,8 @@
       <c r="Y30">
         <v>100</v>
       </c>
-      <c r="Z30" s="1" t="s">
-        <v>29</v>
+      <c r="Z30" s="1">
+        <v>0</v>
       </c>
       <c r="AA30">
         <v>60</v>
@@ -2145,6 +2148,9 @@
       </c>
       <c r="AC30">
         <v>50</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -2232,120 +2238,201 @@
       <c r="AC31">
         <v>95</v>
       </c>
+      <c r="AD31" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>A31+1</f>
         <v>18</v>
       </c>
+      <c r="B32">
+        <v>1060</v>
+      </c>
+      <c r="C32">
+        <v>56</v>
+      </c>
+      <c r="D32">
+        <v>96.427999999999997</v>
+      </c>
+      <c r="E32">
+        <v>94.641999999999996</v>
+      </c>
+      <c r="F32">
+        <v>34</v>
+      </c>
+      <c r="G32">
+        <v>15</v>
+      </c>
+      <c r="H32">
+        <v>40</v>
+      </c>
+      <c r="I32">
+        <v>45</v>
+      </c>
       <c r="K32">
         <f>K31+1</f>
         <v>18</v>
       </c>
+      <c r="L32">
+        <v>1355</v>
+      </c>
+      <c r="M32">
+        <v>69</v>
+      </c>
+      <c r="N32">
+        <v>98.55</v>
+      </c>
+      <c r="O32">
+        <v>98.55</v>
+      </c>
+      <c r="P32">
+        <v>64</v>
+      </c>
+      <c r="Q32">
+        <v>20</v>
+      </c>
+      <c r="R32">
+        <v>62</v>
+      </c>
+      <c r="S32">
+        <v>60</v>
+      </c>
       <c r="U32">
         <f>U31+1</f>
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="V32">
+        <v>1350</v>
+      </c>
+      <c r="W32">
+        <v>75</v>
+      </c>
+      <c r="X32">
+        <v>92</v>
+      </c>
+      <c r="Y32">
+        <v>92</v>
+      </c>
+      <c r="Z32">
+        <v>36</v>
+      </c>
+      <c r="AA32">
+        <v>20</v>
+      </c>
+      <c r="AB32">
+        <v>50</v>
+      </c>
+      <c r="AC32">
+        <v>60</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>AVERAGE(B15:B32)</f>
-        <v>1680</v>
+        <v>1645.5555555555557</v>
       </c>
       <c r="C33">
-        <f t="shared" ref="C33:I33" si="3">AVERAGE(C15:C32)</f>
-        <v>93.411764705882348</v>
+        <f>AVERAGE(C15:C32)</f>
+        <v>91.333333333333329</v>
       </c>
       <c r="D33">
-        <f t="shared" si="3"/>
-        <v>93.361588235294107</v>
+        <f>AVERAGE(D15:D32)</f>
+        <v>93.531944444444434</v>
       </c>
       <c r="E33">
-        <f t="shared" si="3"/>
-        <v>91.369176470588229</v>
+        <f>AVERAGE(E15:E32)</f>
+        <v>91.550999999999988</v>
       </c>
       <c r="F33">
-        <f t="shared" si="3"/>
-        <v>39.235294117647058</v>
+        <f>AVERAGE(F15:F32)</f>
+        <v>38.944444444444443</v>
       </c>
       <c r="G33">
-        <f t="shared" si="3"/>
-        <v>52.352941176470587</v>
+        <f>AVERAGE(G15:G32)</f>
+        <v>50.277777777777779</v>
       </c>
       <c r="H33">
-        <f t="shared" si="3"/>
-        <v>45.176470588235297</v>
+        <f>AVERAGE(H15:H32)</f>
+        <v>44.888888888888886</v>
       </c>
       <c r="I33">
-        <f t="shared" si="3"/>
-        <v>51.294117647058826</v>
+        <f>AVERAGE(I15:I32)</f>
+        <v>50.944444444444443</v>
       </c>
       <c r="L33">
         <f>AVERAGE(L15:L32)</f>
-        <v>1698.5294117647059</v>
+        <v>1679.4444444444443</v>
       </c>
       <c r="M33">
         <f>AVERAGE(M15:M32)</f>
-        <v>94.294117647058826</v>
+        <v>92.888888888888886</v>
       </c>
       <c r="N33">
         <f>AVERAGE(N15:N32)</f>
-        <v>93.476529411764702</v>
+        <v>93.758388888888874</v>
       </c>
       <c r="O33">
-        <f t="shared" ref="O33:S33" si="4">AVERAGE(O15:O32)</f>
-        <v>91.439941176470583</v>
+        <f>AVERAGE(O15:O32)</f>
+        <v>91.834944444444432</v>
       </c>
       <c r="P33">
-        <f t="shared" si="4"/>
-        <v>29.625</v>
+        <f>AVERAGE(P15:P32)</f>
+        <v>30</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="4"/>
-        <v>47.941176470588232</v>
+        <f>AVERAGE(Q15:Q32)</f>
+        <v>46.388888888888886</v>
       </c>
       <c r="R33">
-        <f t="shared" si="4"/>
-        <v>59.705882352941174</v>
+        <f>AVERAGE(R15:R32)</f>
+        <v>59.833333333333336</v>
       </c>
       <c r="S33">
-        <f t="shared" si="4"/>
-        <v>69.117647058823536</v>
+        <f>AVERAGE(S15:S32)</f>
+        <v>68.611111111111114</v>
       </c>
       <c r="V33">
         <f>AVERAGE(V15:V32)</f>
-        <v>1763.2352941176471</v>
+        <v>1740.2777777777778</v>
       </c>
       <c r="W33">
-        <f t="shared" ref="W33:AC33" si="5">AVERAGE(W15:W32)</f>
-        <v>98.588235294117652</v>
+        <f>AVERAGE(W15:W32)</f>
+        <v>97.277777777777771</v>
       </c>
       <c r="X33">
-        <f t="shared" si="5"/>
-        <v>92.440823529411787</v>
+        <f>AVERAGE(X15:X32)</f>
+        <v>92.416333333333355</v>
       </c>
       <c r="Y33">
-        <f t="shared" si="5"/>
-        <v>91.660764705882343</v>
+        <f>AVERAGE(Y15:Y32)</f>
+        <v>91.679611111111114</v>
       </c>
       <c r="Z33">
-        <f t="shared" si="5"/>
-        <v>31.25</v>
+        <f>AVERAGE(Z15:Z32)</f>
+        <v>29.777777777777779</v>
       </c>
       <c r="AA33">
-        <f t="shared" si="5"/>
-        <v>47.352941176470587</v>
+        <f>AVERAGE(AA15:AA32)</f>
+        <v>45.833333333333336</v>
       </c>
       <c r="AB33">
-        <f t="shared" si="5"/>
-        <v>64.058823529411768</v>
+        <f>AVERAGE(AB15:AB32)</f>
+        <v>63.277777777777779</v>
       </c>
       <c r="AC33">
-        <f t="shared" si="5"/>
-        <v>71.470588235294116</v>
-      </c>
-    </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
+        <f>AVERAGE(AC15:AC32)</f>
+        <v>70.833333333333329</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -2353,7 +2440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
         <v>1</v>
       </c>
@@ -2370,7 +2457,7 @@
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <f>B37+1</f>
         <v>2</v>
@@ -2388,9 +2475,9 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
-        <f t="shared" ref="B39:B54" si="6">B38+1</f>
+        <f t="shared" ref="B39:B54" si="3">B38+1</f>
         <v>3</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -2406,9 +2493,9 @@
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -2424,9 +2511,9 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -2442,7 +2529,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
         <f>B41+1</f>
         <v>6</v>
@@ -2460,9 +2547,9 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -2478,9 +2565,9 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -2496,9 +2583,9 @@
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -2514,9 +2601,9 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B46" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2532,9 +2619,9 @@
         <v>0.44500000000000001</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -2550,9 +2637,9 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B48" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -2570,7 +2657,7 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -2588,7 +2675,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -2606,7 +2693,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -2624,7 +2711,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -2642,7 +2729,7 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -2659,24 +2746,27 @@
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="1">
-        <f t="shared" si="6"/>
+      <c r="B54" s="3">
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="3" t="s">
         <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0.38</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="F55">
         <f>AVERAGE(F37:F54)</f>
-        <v>0.47264705882352942</v>
+        <v>0.46750000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Other/Book1.xlsx
+++ b/Other/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DisertationWork\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122A457-1882-4A65-B748-A9511CB78AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF5A772-0ED2-45D5-BB20-C97764551259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F69A984C-CCA6-4246-82C5-767B2FF15A7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="31">
   <si>
     <t>None</t>
   </si>
@@ -2327,105 +2327,102 @@
       <c r="AC32">
         <v>60</v>
       </c>
-      <c r="AD32" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="33" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B33">
-        <f>AVERAGE(B15:B32)</f>
+        <f t="shared" ref="B33:I33" si="3">AVERAGE(B15:B32)</f>
         <v>1645.5555555555557</v>
       </c>
       <c r="C33">
-        <f>AVERAGE(C15:C32)</f>
+        <f t="shared" si="3"/>
         <v>91.333333333333329</v>
       </c>
       <c r="D33">
-        <f>AVERAGE(D15:D32)</f>
+        <f t="shared" si="3"/>
         <v>93.531944444444434</v>
       </c>
       <c r="E33">
-        <f>AVERAGE(E15:E32)</f>
+        <f t="shared" si="3"/>
         <v>91.550999999999988</v>
       </c>
       <c r="F33">
-        <f>AVERAGE(F15:F32)</f>
+        <f t="shared" si="3"/>
         <v>38.944444444444443</v>
       </c>
       <c r="G33">
-        <f>AVERAGE(G15:G32)</f>
+        <f t="shared" si="3"/>
         <v>50.277777777777779</v>
       </c>
       <c r="H33">
-        <f>AVERAGE(H15:H32)</f>
+        <f t="shared" si="3"/>
         <v>44.888888888888886</v>
       </c>
       <c r="I33">
-        <f>AVERAGE(I15:I32)</f>
+        <f t="shared" si="3"/>
         <v>50.944444444444443</v>
       </c>
       <c r="L33">
-        <f>AVERAGE(L15:L32)</f>
+        <f t="shared" ref="L33:S33" si="4">AVERAGE(L15:L32)</f>
         <v>1679.4444444444443</v>
       </c>
       <c r="M33">
-        <f>AVERAGE(M15:M32)</f>
+        <f t="shared" si="4"/>
         <v>92.888888888888886</v>
       </c>
       <c r="N33">
-        <f>AVERAGE(N15:N32)</f>
+        <f t="shared" si="4"/>
         <v>93.758388888888874</v>
       </c>
       <c r="O33">
-        <f>AVERAGE(O15:O32)</f>
+        <f t="shared" si="4"/>
         <v>91.834944444444432</v>
       </c>
       <c r="P33">
-        <f>AVERAGE(P15:P32)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="Q33">
-        <f>AVERAGE(Q15:Q32)</f>
+        <f t="shared" si="4"/>
         <v>46.388888888888886</v>
       </c>
       <c r="R33">
-        <f>AVERAGE(R15:R32)</f>
+        <f t="shared" si="4"/>
         <v>59.833333333333336</v>
       </c>
       <c r="S33">
-        <f>AVERAGE(S15:S32)</f>
+        <f t="shared" si="4"/>
         <v>68.611111111111114</v>
       </c>
       <c r="V33">
-        <f>AVERAGE(V15:V32)</f>
+        <f t="shared" ref="V33:AC33" si="5">AVERAGE(V15:V32)</f>
         <v>1740.2777777777778</v>
       </c>
       <c r="W33">
-        <f>AVERAGE(W15:W32)</f>
+        <f t="shared" si="5"/>
         <v>97.277777777777771</v>
       </c>
       <c r="X33">
-        <f>AVERAGE(X15:X32)</f>
+        <f t="shared" si="5"/>
         <v>92.416333333333355</v>
       </c>
       <c r="Y33">
-        <f>AVERAGE(Y15:Y32)</f>
+        <f t="shared" si="5"/>
         <v>91.679611111111114</v>
       </c>
       <c r="Z33">
-        <f>AVERAGE(Z15:Z32)</f>
+        <f t="shared" si="5"/>
         <v>29.777777777777779</v>
       </c>
       <c r="AA33">
-        <f>AVERAGE(AA15:AA32)</f>
+        <f t="shared" si="5"/>
         <v>45.833333333333336</v>
       </c>
       <c r="AB33">
-        <f>AVERAGE(AB15:AB32)</f>
+        <f t="shared" si="5"/>
         <v>63.277777777777779</v>
       </c>
       <c r="AC33">
-        <f>AVERAGE(AC15:AC32)</f>
+        <f t="shared" si="5"/>
         <v>70.833333333333329</v>
       </c>
       <c r="AD33" t="s">
@@ -2477,7 +2474,7 @@
     </row>
     <row r="39" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
-        <f t="shared" ref="B39:B54" si="3">B38+1</f>
+        <f t="shared" ref="B39:B54" si="6">B38+1</f>
         <v>3</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -2495,7 +2492,7 @@
     </row>
     <row r="40" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -2513,7 +2510,7 @@
     </row>
     <row r="41" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -2549,7 +2546,7 @@
     </row>
     <row r="43" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -2567,7 +2564,7 @@
     </row>
     <row r="44" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -2585,7 +2582,7 @@
     </row>
     <row r="45" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -2603,7 +2600,7 @@
     </row>
     <row r="46" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B46" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2621,7 +2618,7 @@
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -2639,7 +2636,7 @@
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B48" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -2657,7 +2654,7 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -2675,7 +2672,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -2693,7 +2690,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -2711,7 +2708,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -2729,7 +2726,7 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -2747,7 +2744,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="C54" s="3" t="s">
